--- a/GenData/events_predicted_df.xlsx
+++ b/GenData/events_predicted_df.xlsx
@@ -135,7 +135,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -154,6 +154,10 @@
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -391,14 +395,14 @@
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="5" t="n">
         <v>2</v>
       </c>
       <c r="B4" s="3" t="n">
-        <v>297.1</v>
+        <v>296.2</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>297.1</v>
+        <v>297.7</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>5</v>

--- a/GenData/events_predicted_df.xlsx
+++ b/GenData/events_predicted_df.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
-  <fileVersion appName="Calc" lowestEdited="7"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId2"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="6">
   <si>
     <t xml:space="preserve">time_start</t>
   </si>
@@ -50,7 +50,7 @@
   <fonts count="6">
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
@@ -80,7 +80,7 @@
     <font>
       <b val="true"/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
@@ -172,188 +172,13 @@
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
-  <a:themeElements>
-    <a:clrScheme name="Office">
-      <a:dk1>
-        <a:srgbClr val="000000"/>
-      </a:dk1>
-      <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
-      </a:lt1>
-      <a:dk2>
-        <a:srgbClr val="1F497D"/>
-      </a:dk2>
-      <a:lt2>
-        <a:srgbClr val="EEECE1"/>
-      </a:lt2>
-      <a:accent1>
-        <a:srgbClr val="4F81BD"/>
-      </a:accent1>
-      <a:accent2>
-        <a:srgbClr val="C0504D"/>
-      </a:accent2>
-      <a:accent3>
-        <a:srgbClr val="9BBB59"/>
-      </a:accent3>
-      <a:accent4>
-        <a:srgbClr val="8064A2"/>
-      </a:accent4>
-      <a:accent5>
-        <a:srgbClr val="4BACC6"/>
-      </a:accent5>
-      <a:accent6>
-        <a:srgbClr val="F79646"/>
-      </a:accent6>
-      <a:hlink>
-        <a:srgbClr val="0000FF"/>
-      </a:hlink>
-      <a:folHlink>
-        <a:srgbClr val="800080"/>
-      </a:folHlink>
-    </a:clrScheme>
-    <a:fontScheme name="Office">
-      <a:majorFont>
-        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-      </a:majorFont>
-      <a:minorFont>
-        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-      </a:minorFont>
-    </a:fontScheme>
-    <a:fmtScheme>
-      <a:fillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="35000">
-              <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
-        </a:gradFill>
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
-        </a:gradFill>
-      </a:fillStyleLst>
-      <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </a:lnStyleLst>
-      <a:effectStyleLst>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-      </a:effectStyleLst>
-      <a:bgFillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="40000">
-              <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
-        </a:gradFill>
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
-        </a:gradFill>
-      </a:bgFillStyleLst>
-    </a:fmtScheme>
-  </a:themeElements>
-</a:theme>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D79"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B1" s="1" t="s">
@@ -409,14 +234,32 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4"/>
-      <c r="B5" s="3"/>
-      <c r="D5" s="3"/>
+      <c r="A5" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>298</v>
+      </c>
+      <c r="C5" s="0" t="n">
+        <v>298</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4"/>
-      <c r="B6" s="3"/>
-      <c r="D6" s="3"/>
+      <c r="A6" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>298.2</v>
+      </c>
+      <c r="C6" s="0" t="n">
+        <v>299.4</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4"/>
